--- a/Ministry_of_Interior_and_Municipalities.xlsx
+++ b/Ministry_of_Interior_and_Municipalities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1195,6 +1195,2315 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/28/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>قام وزير الداخلية والبلديات احمد الحجار بزيارة تفقدية الى مدينة جونية حيث كان في إستقباله محافظ جبل لبنان القاضي محمد مكاوي ، قائمقام كسروان الفتوح ستريدا نبهان ، رئيس اتحاد بلديات كسروان الفتوح الياس بعينو ، رئيس بلدية جونية فيصل إفرام وشخصيات بلدية وأمنية وعسكرية.بدأ الوزير الحجار جولته بجولة مع</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:33.053443+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>كلمة الوزير احمد الحجار خلال لقاء حواري مع رؤساء بلديات كسروان الفتوح في بلدية جونية</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d9%83%d9%84%d9%85%d8%a9-%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d8%ad%d9%85%d8%af-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%ae%d9%84%d8%a7%d9%84-%d9%84%d9%82%d8%a7%d8%a1-%d8%ad%d9%88%d8%a7%d8%b1/</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>قام وزير الداخلية والبلديات احمد الحجار بزيارة تفقدية الى مدينة جونية حيث كان في إستقباله محافظ جبل لبنان القاضي محمد مكاوي ، قائمقام كسروان الفتوح ستريدا نبهان ، رئيس اتحاد بلديات كسروان الفتوح الياس بعينو ، رئيس بلدية جونية فيصل إفرام وشخصيات بلدية وأمنية وعسكرية.
+بدأ الوزير الحجار جولته بجولة مع الحضور في أسواق جونية، وإستمع الى المواطنين بعدها توجه سيرا على الأقدام الى مبنى البلدية حيث عقد لقاء مع رؤساء بلديات المنطقة، بحضور المدير العام للإدارات والمجالس المحلية فاتن ابو الحسن بعنوان : “من الإجراءات الى الإنجاز: شراكة تسرع العمل البلدي بهدف تعزيز التعاون بين الوزارة والبلديات وتسريع العمل البلدي “.
+وخلال اللقاء تحدث الوزير الحجار قائلا: “يسعدني أن أكون بينكم اليوم في بلدية جونية، في إطار حرصنا على تعزيز التواصل المباشر مع البلديات، والاستماع إلى هواجسها واحتياجاتها، ومتابعة التحديات التي تواجهها في أداء مهامها. وأتوجّه بالشكر إلى بلدية جونية وإلى محافظ جبل لبنان على هذه المبادرة، التي تشكل فرصة للحوار والتعاون وتبادل الأراء حول سبل تطوير العمل البلدي”.
+واكد ان” جونية، عاصمة قضاء كسروان، تُشكّل واجهةً حيويةً للبنان، بما تختزنه من تاريخ عريق، وموقعٍ ساحلي مميّز، ودور اقتصادي وسياحي وثقافي بارز. أمّا قضاء كسروان، بما يضمّه من بلدات وقرى عريقة ومتنوّعة، فيجسّد غنى لبنان وتنوّعه، ويتميّز بحيوية أبنائه وتمسّكهم بأرضهم وانتمائهم لوطنهم.
+ومن جونية، نؤكّد اليوم أهمية دور البلديات في تعزيز الإنماء المحلي، وصون خصوصية المنطقة، والاستجابة لتطلّعات المواطنين، من خلال التعاون والتنسيق لما فيه خير كسروان ولبنان”.
+أضاف:”إنّ البلديات هي خط الدفاع الأول في خدمة المواطن، وهي شريك أساسي لوزارة الداخلية والبلديات في تعزيز الإنماء المحلي، وترسيخ الاستقرار، وتحسين الخدمات العامة.
+ومن هنا، نؤكد أهمية التعاون والتنسيق المستمر بين الوزارة والبلديات، بما يتيح تجاوز الصعوبات وتحقيق المصلحة العامة، بعيدًا من كل اعتبار، وانطلاقًا من مسؤوليتنا المشتركة تجاه أهلنا ووطننا”.
+واشار الى ان” البلديات هي السلطة الأقرب إلى المواطنين، وهي خطّ التواصل الأول معهم، والمسؤولة عن تلبية جانب أساسي من حاجاتهم اليومية. وقد برزت أهمية هذا الدور بصورة خاصة خلال الأزمات التي مرّ بها لبنان، ولا سيما خلال الأزمة الأخيرة وموجات النزوح، حيث تحمّلت البلديات مسؤوليات كبيرة في الاستجابة للحاجات الطارئة، وتأمين الخدمات الأساسية، ومواكبة المواطنين والنازحين، غالباً في ظل إمكانات محدودة وضغوط استثنائية”.
+ورأى “إنّ دعم البلديات وتعزيز قدرتها على القيام بمهامها يشكّلان أولوية أساسية. وهذا الدعم لا يقتصر على تأمين الموارد المالية، بل يشمل أيضاً تحسين الإدارة، وتطوير الكفاءات، وتحديث آليات العمل، وتعزيز التنسيق بين مختلف الجهات المعنية”.
+وتابع الوزير الحجار :”وفي هذا الإطار، لا بدّ من العمل على انتظام التحويلات المالية المستحقة للباديات، ولا سيما من الصندوق البلدي المستقل، ومتابعة ملف عائدات الخليوي، بما يساهم في تمكين البلديات من تنفيذ مشاريعها والوفاء بالتزاماتها تجاه المواطنين. كما أنّ تحسين جباية الرسوم البلدية يشكّل عنصراً أساسياً في تعزيز الموارد الذاتية، شرط أن يقترن بحسن الإدارة والشفافية والحرص على العدالة في تطبيق القوانين. كذلك، نولي أهمية كبيرة للاستثمار في العنصر البشري، من خلال تعزيز قدرات رؤساء البلديات وأعضاء المجالس البلدية والموظفين والشرطة البلدية، وتطوير مهاراتهم في الإدارة المالية، وإعداد الموازنات، وإدارة المشاريع، وتطبيق القوانين والأنظمة. ويمكن تحقيق ذلك من خلال برامج تدريبية متخصصة، بالشراكة مع المعهد الوطني للإدارة، ومعهد باسل فليحان المالي والاقتصادي، والجامعات الخاصة، ومعهد قوى الأمن الداخلي”.
+وعلى صعيد الخدمات البلدية، لفت إلى” أهمية تطبيق قانون الإدارة المتكاملة للنفايات الصلبة رقم 80 تاريخ 10 تشرين الأول 2018، والعمل على اعتماد حلول مستدامة لإدارة النفايات، تراعي المعايير البيئية والصحية وتستجيب لحاجات البلدياتوخصوصياتها”.
+واكد ان” ملف الأمن والسلامة المرورية وتنظيم السير، لا يقلّ عن ذلك أهميةً ، حيث تؤدي الشرطة البلدية دوراً أساسياً في الحفاظ على النظام العام المحلي، ضمن صلاحياتها القانونية، وبالتنسيق المستمر مع قوى الأمن الداخلي، بما يعزّز سلامة المواطنين ويساهم في تحسين جودة الحياة في المدن والبلدات ، وينظم العلاقة بين الشرطة البلدية وقوى الامن مما ينعكس ايجابياً على الأمن ضمن رؤية الوزارة والحكومة لبسط سلطة الدولة، وهنا أكرر الشعار الدي صدر مني عفويا واعتقد اننا نتفق عليه جميعا وهو : ” شعب واحد ، جيش واحد ، دولة واحدة ” وهذا هو المسار الوحيد ليخلص لبنان من أزماته”.
+وختم الوزير الحجار بالقول: ” إنّ وزارة الداخلية والبلديات تقدّر الدور الذي تقومون به، وتدرك حجم المسؤوليات الملقاة على عاتقكم والتحديات التي تواجهونها يومياً. وأودّ أن أؤكد لكم أنّ الوزارة إلى جانبكم، وهي مستعدة لمواكبتكم ومتابعة مختلف الملفات معكم، والعمل، قدر الإمكان وضمن الإمكانات المتاحة والصلاحيات القانونية، على تذليل العقبات التي تعترض عملكم ففي نهاية المطاف، نحن وإياكم فريق واحد، وهدفنا مشترك: خدمة أهلنا، وتحسين ظروف حياتهم في بلداتهم، وتعزيز قدرة البلديات على القيام بمهامها والاستجابة لحاجات المواطنين وتطلعاتهم.
+أشكركم مجدداً على حسن الاستقبال، وأتطلع إلى أن يشكّل لقاؤنا اليوم خطوة إضافية نحو تعاون أكثر فاعلية، وشراكة عملية بين الوزارة والبلديات، لما فيه خير جونية وكسروان-الفتوح وأهلها، وخير جميع اللبنانيين”.
+بعدها كان حوار ومناقشة مع رؤساء البلديات ورد على أسئلتهم وهمومهم البلدية.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:36.036651+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/27/</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>أجرى وزير الداخلية والبلديات أحمد الحجار اتصالا هاتفيا، بنظيره الأردني مازن الفراية، معزيا بضحايا الحادث الإرهابي الأليم الذي استهدف كنيسة القديس جاورجيوس في قرية حمود في محافظة الكرك، مؤكدا “تضامن لبنان مع الأردن في هذا المصاب”، سائلاً الرحمة للضحايا والصبر والسلوان لذويهم.ودان الوزير الحجار “العمل الإرهابي الذي استهدف المصلّين”، مشددا
+الوزير الحجار استقبل سفير العراق محمد رضا الحسيني ثم سفير لبنان في باكستان عبد العزيز عيسى، والتقى النائب وليد البعريني ثم وفدا من أصحاب شركات الإعلانات
+استقبل وزير الداخلية والبلديات أحمد الحجار، سفير العراق محمد رضا الحسيني، وجرى البحث في العلاقات الثنائية بين البلدين وسبل تطويرها وتعزيز التعاون المشترك في مختلف المجالات. كما استقبل سفير لبنان في جمهورية باكستان الإسلامية عبد العزيز عيسى، وتم التداول في عدد من المواضيع المتصلة بالعلاقات اللبنانية – الباكستانية. والتقى الوزير</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:38.705819+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>الوزير الحجار اتصل بنظيره الأردني معزيا بضحايا الحادث الارهابي</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%aa%d8%b5%d9%84-%d8%a8%d9%86%d8%b8%d9%8a%d8%b1%d9%87-%d8%a7%d9%84%d8%a3%d8%b1%d8%af%d9%86%d9%8a-%d9%85%d8%b9%d8%b2/</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>أجرى وزير الداخلية والبلديات أحمد الحجار اتصالا هاتفيا، بنظيره الأردني مازن الفراية، معزيا بضحايا الحادث الإرهابي الأليم الذي استهدف كنيسة القديس جاورجيوس في قرية حمود في محافظة الكرك، مؤكدا “تضامن لبنان مع الأردن في هذا المصاب”، سائلاً الرحمة للضحايا والصبر والسلوان لذويهم.
+ودان الوزير الحجار “العمل الإرهابي الذي استهدف المصلّين”، مشددا على “رفض كل أشكال الإرهاب والعنف التي تطال الأبرياء”، مؤكدا “ضرورة تضافر الجهود لمواجهة هذه الأعمال وصون أمن المجتمعات واستقرارها”.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:41.335446+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل سفير العراق محمد رضا الحسيني ثم سفير لبنان في باكستان عبد العزيز عيسى، والتقى النائب وليد البعريني ثم وفدا من أصحاب شركات الإعلانات</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b3%d9%81%d9%8a%d8%b1-%d8%a7%d9%84%d8%b9%d8%b1%d8%a7%d9%82-%d9%85%d8%ad%d9%85%d8%af/</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، سفير العراق محمد رضا الحسيني، وجرى البحث في العلاقات الثنائية بين البلدين وسبل تطويرها وتعزيز التعاون المشترك في مختلف المجالات.
+كما استقبل سفير لبنان في جمهورية باكستان الإسلامية عبد العزيز عيسى، وتم التداول في عدد من المواضيع المتصلة بالعلاقات اللبنانية – الباكستانية.
+والتقى الوزير الحجار النائب وليد البعريني، وتناول البحث شؤونا إنمائية وخدماتية، إلى جانب عدد من القضايا المتصلة بمنطقة عكار وحاجات أهلها.
+وكذلك، استقبل وفدا من أصحاب شركات الإعلانات، عرض خلال اللقاء واقع القطاع والتحديات التي تواجهه.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:43.991393+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/26/</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، الوزير السابق زياد بارود، وجرى البحث في الأوضاع العامة على الساحة الداخلية والتطورات الراهنة. واطلع من محافظ مدينة بيروت القاضي مروان عبود على أوضاع العاصمة وشؤونها، والملفات البلدية والإدارية المطروحة.وتناول اللقاء واقع البنية التحتية والخدمات العامة في العاصمة، وسائر الملفات الخدماتية والإنمائية. والتقى الوزير</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:46.564817+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل الوزير السابق زياد بارود ثم محافظ مدينة بيروت القاضي مروان عبود والتقى النائب السابق نبيل نقولا ثم رئيسة جمعية “أجيالنا” لينا الزعيم الدادا وأعضاء الهيئة الإدارية للجمعية.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%b3%d8%a7%d8%a8%d9%82-%d8%b2%d9%8a/</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، الوزير السابق زياد بارود، وجرى البحث في الأوضاع العامة على الساحة الداخلية والتطورات الراهنة.
+واطلع من محافظ مدينة بيروت القاضي مروان عبود على أوضاع العاصمة وشؤونها، والملفات البلدية والإدارية المطروحة.
+وتناول اللقاء واقع البنية التحتية والخدمات العامة في العاصمة، وسائر الملفات الخدماتية والإنمائية.
+والتقى الوزير الحجار النائب السابق نبيل نقولا، وتناول اللقاء شؤونا عامة.
+كذلك، استقبل رئيسة جمعية “أجيالنا” لينا الزعيم الدادا وأعضاء الهيئة الإدارية للجمعية، وجرى التداول في شؤون تتصل بعمل الجمعية ونشاطاتها، والبرامج التي تنفذها في إطار رسالتها الاجتماعية.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:49.224033+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/25/</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>أجرى وزير الداخلية والبلديات أحمد الحجار اتصالا بنظيره السعودي الأمير عبد العزيز بن سعود بن نايف بن عبدالعزيز آل سعود، في إطار التواصل والتشاور في شأن التطورات الراهنة في المنطقة. وأكد الوزير الحجار “تضامن لبنان الكامل مع السعودية ووقوفه إلى جانبها ودعمه لكل ما من شأنه الحفاظ على أمنها واستقرارها</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:56.893201+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>الوزير الحجار اتصل بنظيره السعودي متضامنا: ندعم كل ما من شأنه الحفاظ على أمن المملكة وسلامة أراضيها</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%aa%d8%b5%d9%84-%d8%a8%d9%86%d8%b8%d9%8a%d8%b1%d9%87-%d8%a7%d9%84%d8%b3%d8%b9%d9%88%d8%af%d9%8a-%d9%85%d8%aa%d8%b6/</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>أجرى وزير الداخلية والبلديات أحمد الحجار اتصالا بنظيره السعودي الأمير عبد العزيز بن سعود بن نايف بن عبدالعزيز آل سعود، في إطار التواصل والتشاور في شأن التطورات الراهنة في المنطقة.
+وأكد الوزير الحجار “تضامن لبنان الكامل مع السعودية ووقوفه إلى جانبها ودعمه لكل ما من شأنه الحفاظ على أمنها واستقرارها وسلامة أراضيها”.
+وشكر الوزير الحجار لنظيره السعودي “وقوف المملكة الدائم إلى جانب لبنان، وما تقدمه من دعم ومساندة”، مثمناً “مواقفها الأخوية التي تعكس عمق العلاقات التاريخية التي تجمع البلدين والشعبين الشقيقين”.
+كما تناول الاتصال سبل تعزيز التعاون والتنسيق المشترك بين وزارتي الداخلية في البلدين، لا سيما في المجالات الأمنية، بما يساهم في مواجهة التحديات المشتركة وترسيخ الأمن والاستقرار.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:59.834065+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/24/</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>رافق وزير الداخلية والبلديات أحمد الحجار رئيس الجمهورية العماد جوزاف عون في زيارته إلى مدينة طرابلس اليوم، حيث كان في استقباله في سرايا المدينة.وأكد الوزير الحجار أن طرابلس مدينة عزيزة على قلوب جميع اللبنانيين، وعلى قلب رئيس الجمهورية والحكومة.إن وجود فخامة الرئيس في المدينة يؤكد اهتمام الدولة بطرابلس وحرصها على</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:07.487359+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>الوزير الحجار رافق رئيس الجمهورية العماد جوزاف عون في زيارته إلى مدينة طرابلس.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%b1%d8%a7%d9%81%d9%82-%d8%b1%d8%a6%d9%8a%d8%b3-%d8%a7%d9%84%d8%ac%d9%85%d9%87%d9%88%d8%b1%d9%8a%d8%a9-%d8%a7%d9%84%d8%b9/</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>رافق وزير الداخلية والبلديات أحمد الحجار رئيس الجمهورية العماد جوزاف عون في زيارته إلى مدينة طرابلس اليوم، حيث كان في استقباله في سرايا المدينة.
+وأكد الوزير الحجار أن طرابلس مدينة عزيزة على قلوب جميع اللبنانيين، وعلى قلب رئيس الجمهورية والحكومة.
+إن وجود فخامة الرئيس في المدينة يؤكد اهتمام الدولة بطرابلس وحرصها على متابعة شؤونها عن قرب.
+وتوجه لأهالي مدينة طرابلس بالقول: “أهلنا في طرابلس، نحن جميعًا إلى جانبكم، ونتابع شؤونكم.
+ونأمل أن تكون هذه المرحلة فاتحة خير لمدينة طرابلس، على الصعيد الأمني والاقتصادي والإنمائي، وعلى جميع الأصعدة.”</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:10.466448+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/23/</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار سفير جمهورية مصر العربية تميم خلاف، في زيارة تعارف.وخلال اللقاء، تم البحث في العلاقات الثنائية بين البلدين وسبل تعزيزها وتطوير آفاق التعاون المشترك، لا سيما في المجالات الأمنية. كما التقى الوزير الحجار النائب فيصل الصايغ، حيث تناول البحث شؤون العاصمة بيروت وأوضاع أهلها.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:17.962341+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل سفير جمهورية مصر العربية تميم خلاف ثم النائب فيصل الصايغ.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b3%d9%81%d9%8a%d8%b1-%d8%ac%d9%85%d9%87%d9%88%d8%b1%d9%8a%d8%a9-%d9%85%d8%b5%d8%b1/</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار سفير جمهورية مصر العربية تميم خلاف، في زيارة تعارف.
+وخلال اللقاء، تم البحث في العلاقات الثنائية بين البلدين وسبل تعزيزها وتطوير آفاق التعاون المشترك، لا سيما في المجالات الأمنية.
+كما التقى الوزير الحجار النائب فيصل الصايغ، حيث تناول البحث شؤون العاصمة بيروت وأوضاع أهلها.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:21.002148+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/21/</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>عقد وزير الداخلية والبلديات أحمد الحجار، في الدوحة، سلسلة لقاءات على هامش مشاركته في المعرض العالمي للأمن الداخلي والسلامة “ميليبول قطر 2026″،شملت وزير داخلية بلجيكا برنارد كوينتين، ووزير الدولة في وزارة الداخلية الألمانية بيرند كروسر، ووزير العدل والنظام العام في قبرص كوستاس فيتيريس، وذلك في حضور سفير لبنان في قطر</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:23.645254+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>الوزير الحجار عقد في الدوحة، سلسلة لقاءات شملت وزير داخلية بلجيكا برنارد كوينتين، ووزير الدولة في وزارة الداخلية الألمانية بيرند كروسر، ووزير العدل والنظام العام في قبرص كوستاس فيتيريس</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%b9%d9%82%d8%af-%d9%81%d9%8a-%d8%a7%d9%84%d8%af%d9%88%d8%ad%d8%a9%d8%8c-%d8%b3%d9%84%d8%b3%d9%84%d8%a9-%d9%84%d9%82%d8%a7/</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>عقد وزير الداخلية والبلديات أحمد الحجار، في الدوحة، سلسلة لقاءات على هامش مشاركته في المعرض العالمي للأمن الداخلي والسلامة “ميليبول قطر 2026″،
+شملت وزير داخلية بلجيكا برنارد كوينتين، ووزير الدولة في وزارة الداخلية الألمانية بيرند كروسر، ووزير العدل والنظام العام في قبرص كوستاس فيتيريس، وذلك في حضور سفير لبنان في قطر بلال قبلان وأمين سر مجلس الامن الداخلي المركزي العميد سامي ناصيف.
+وتناول الوزير الحجار مع المسؤولين الذين التقاهم سبل تعزيز العلاقات والتعاون في المجالات الأمنية، وتطوير آليات التنسيق في ظل التحديات الأمنية في المنطقة والتي تستدعي تكثيف التعاون بين الدول وتوحيد الجهود لمواجهتها.
+كما شكّلت اللقاءات مناسبة لعرض التحديات التي يواجهها لبنان في المرحلة الراهنة، والتشديد على أهمية دعم المؤسسات الأمنية اللبنانية وتعزيز قدراتها، بما يمكّنها من تعزيز دورها والقيام بمهامها في حفظ الأمن والاستقرار.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:26.377910+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/20/</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>أطلق وزير الداخلية والبلديات أحمد الحجار، من السفارة اللبنانية في قطر، خدمة البصمة البيومترية لإصدار جوازات السفر البيومترية، بحضور سفير لبنان في قطر بلال قبلان، نائب رئيس البعثة القنصل شانت فارتانيان، وفد من الأمن العام اللبناني وطاقم السفارة.وأكد الوزير الحجار أن “هذه الخدمة ستعمّم تباعا على السفارات والقنصليات اللبنانية في
+عقد وزير الداخلية والبلديات أحمد الحجار لقاء مع وزير الداخلية وقائد قوة الأمن الداخلي “لخويا” الشيخ خليفة بن حمد بن خليفة آل ثاني
+عقد وزير الداخلية والبلديات أحمد الحجار لقاء مع وزير الداخلية وقائد قوة الأمن الداخلي “لخويا” الشيخ خليفة بن حمد بن خليفة آل ثاني، في حضور أمين سر مجلس الامن الداخلي المركزي العميد سامي ناصيف.وتمت مناقشة المواضيع ذات الاهتمام المشترك، واستعراض علاقات التعاون بين البلدين الشقيقين في المجالات الأمنية وسبل دعمها
+الوزير الحجار شارك في افتتاح معرض “ميليبول قطر 2026” للأمن الداخلي والسلامة والتقى اللبنانيين المشاركين فيه مثنيا على دورهم المتميز وحضورهم اللافت
+شارك وزير الداخلية والبلديات أحمد الحجار في افتتاح فعاليات المعرض العالمي للأمن الداخلي والسلامة “ميليبول قطر 2026″، الذي أُقيم في مركز الدوحة للمعارض والمؤتمرات (DECC)، بحضور وزير الداخلية وقائد قوة الأمن الداخلي “لخويا” الشيخ خليفة بن حمد بن خليفة آل ثاني.ويجمع المعرض كبرى الشركات العالمية ونخبة من الخبراء والمتخصصين في</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:29.007142+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>الوزير الحجار أطلق خدمة البصمة البيومترية في السفارة اللبنانية في قطر والتقى الجالية: الدولة عازمة على بسط سلطتها على كامل أراضيها</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a3%d8%b7%d9%84%d9%82-%d8%ae%d8%af%d9%85%d8%a9-%d8%a7%d9%84%d8%a8%d8%b5%d9%85%d8%a9-%d8%a7%d9%84%d8%a8%d9%8a%d9%88%d9%85/</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>أطلق وزير الداخلية والبلديات أحمد الحجار، من السفارة اللبنانية في قطر، خدمة البصمة البيومترية لإصدار جوازات السفر البيومترية، بحضور سفير لبنان في قطر بلال قبلان، نائب رئيس البعثة القنصل شانت فارتانيان، وفد من الأمن العام اللبناني وطاقم السفارة.
+وأكد الوزير الحجار أن “هذه الخدمة ستعمّم تباعا على السفارات والقنصليات اللبنانية في دول الخليج وسائر دول العالم، بالتنسيق مع وزارة الخارجية والمغتربين، بما يتيح للبنانيين المقيمين في الخارج إنجاز معاملاتهم بسهولة”، وقال: “بعد إطلاق هذه الخدمة في الكويت وباريس وديترويت وواشنطن، نطلقها اليوم في قطر، هذه الدولة التي تحتضن جالية لبنانية كبيرة تضم كفاءات متميّزة وطاقات ناجحة في مختلف المجالات والقطاعات، وتساهم في نهضة المجتمع الذي تعيش فيه، وترفع اسم لبنان عاليا”.
+وفي دارة السفير، التقى الوزير الحجار عددا من أبناء الجالية اللبنانية، واستمع إلى مطالبهم وهواجسهم، وقال: “نواجه اليوم واقعا صعبا، في ظل استمرار الاحتلال الإسرائيلي والاعتداءات اليومية على جنوب لبنان، مما يفرض تحديات كبيرة، إلا أن الدولة عازمة على بسط سلطتها على كامل أراضيها، وتهيئة الظروف الملائمة لعودة الاهالي النازحين إلى قراهم وبلداتهم”.
+أضاف: “علينا أن نعمل على تهيئة الظروف التي تتيح للبنانيين العودة إلى وطنهم والمساهمة في نهضته، فنحن نثق بلبنان وبقدرة أبنائه على النهوض مجددا”.
+وأكد أن “الدولة اتخذت خيار المضي باتجاه المفاوضات، بمساعدة الولايات المتحدة الأميركية”، وقال: “نحن ندرك أن هذا المسار شائك وصعب، لكن علينا بذل كل جهد ممكن لتحرير الأرض وإنهاء الاحتلال”.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:31.581450+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>عقد وزير الداخلية والبلديات أحمد الحجار لقاء مع وزير الداخلية وقائد قوة الأمن الداخلي “لخويا” الشيخ خليفة بن حمد بن خليفة آل ثاني</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%b9%d9%82%d8%af-%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%af%d8%a7%d8%ae%d9%84%d9%8a%d8%a9-%d9%88%d8%a7%d9%84%d8%a8%d9%84%d8%af%d9%8a%d8%a7%d8%aa-%d8%a3%d8%ad%d9%85%d8%af-%d8%a7%d9%84%d8%ad%d8%ac/</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>عقد وزير الداخلية والبلديات أحمد الحجار لقاء مع وزير الداخلية وقائد قوة الأمن الداخلي “لخويا” الشيخ خليفة بن حمد بن خليفة آل ثاني، في حضور أمين سر مجلس الامن الداخلي المركزي العميد سامي ناصيف.
+وتمت مناقشة المواضيع ذات الاهتمام المشترك، واستعراض علاقات التعاون بين البلدين الشقيقين في المجالات الأمنية وسبل دعمها وتطويرها.
+وشكر الوزير الحجار لنظيره القطري دعم دولة قطر الدائم للبنان، مثمّنا وقوفها إلى جانبه، ومؤكدا أهمية التضامن العربي في ظل الظروف الدقيقة التي تمر بها المنطقة.
+واتفق الوزيران على تشكيل لجنة أمنية مشتركة بين وزارتي الداخلية في البلدين، تتولى متابعة ملفات التعاون الأمني المشترك، وتنسيق الجهود وتطوير آليات التعاون وتبادل الخبرات، بما يخدم المصالح المشتركة ويعزز الأمن والاستقرار في البلدين الشقيقين.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:37.060716+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>الوزير الحجار شارك في افتتاح معرض “ميليبول قطر 2026” للأمن الداخلي والسلامة والتقى اللبنانيين المشاركين فيه مثنيا على دورهم المتميز وحضورهم اللافت</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%b4%d8%a7%d8%b1%d9%83-%d9%81%d9%8a-%d8%a7%d9%81%d8%aa%d8%aa%d8%a7%d8%ad-%d9%85%d8%b9%d8%b1%d8%b6-%d9%85%d9%8a%d9%84%d9%8a/</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>شارك وزير الداخلية والبلديات أحمد الحجار في افتتاح فعاليات المعرض العالمي للأمن الداخلي والسلامة “ميليبول قطر 2026″، الذي أُقيم في مركز الدوحة للمعارض والمؤتمرات (DECC)، بحضور وزير الداخلية وقائد قوة الأمن الداخلي “لخويا” الشيخ خليفة بن حمد بن خليفة آل ثاني.
+ويجمع المعرض كبرى الشركات العالمية ونخبة من الخبراء والمتخصصين في مجالات الأمن والسلامة، لاستعراض أحدث التقنيات والحلول الأمنية، ومناقشة التحديات الراهنة واستشراف مستقبل الأمن الداخلي، إلى جانب تبادل الخبرات والتجارب بين الدول والمؤسسات المعنية.
+وكانت فرصة للوزير الحجار للقيام بجولة على أجنحة المعرض، حيث التقى عددا من اللبنانيين المشاركين، واستمع إلى شروحات حول طبيعة مشاركاتهم وأهمية حضورهم في هذا الحدث الدولي الذي يجمع مسؤولين وخبراء ومؤسسات متخصصة في تطوير القدرات الأمنية والتكنولوجية وتعزيز التعاون وتبادل الخبرات.
+وأعرب الوزير الحجار عن تقديره للدور الريادي للبنانيين، لا سيما الشابات والشباب منهم في مختلف المجالات، مثمّنا حضورهم الفاعل واللافت ودورهم المتميز في الفعاليات العربية والدولية، وما يعكسه ذلك من كفاءة وخبرة وقدرة على مواكبة التطورات والابتكار.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:39.682347+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/19/</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>وصل وزير الداخلية والبلديات أحمد الحجار إلى دولة قطر، للمشاركة في فعاليات المعرض العالمي للأمن الداخلي والسلامة “ميليبول قطر 2026″، بدعوة من وزير الداخلية وقائد قوة الأمن الداخلي “لخويا” الشيخ خليفة بن حمد بن خليفة آل ثاني. ومن المقرر أن يعقد الوزير الحجار سلسلة لقاءات مع عدد من المسؤولين ونظرائه
+الوزير الحجار وضع إكليلا من الزهر على ضريح اللواء الشهيد وسام الحسن
+وضع وزير الداخلية والبلديات أحمد الحجار، ممثلا بأمين سر مجلس الأمن الداخلي المركزي العميد سامي ناصيف، إكليلا من الزهر على ضريح اللواء الشهيد وسام الحسن، في ذكرى استشهاده، تقديرا لتضحياته وتضحيات رفيقه المؤهل أول أحمد صهيوني. وقال الوزير الحجار: في ذكرى استشهاد اللواء وسام الحسن، نستذكر رجلا كرّس حياته لحماية</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:42.266763+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>الوزير الحجار وصل إلى الدوحة للمشاركة في “ميليبول 2026” وعقد لقاء مع نظيره الباكستاني</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d9%88%d8%b5%d9%84-%d8%a5%d9%84%d9%89-%d8%a7%d9%84%d8%af%d9%88%d8%ad%d8%a9-%d9%84%d9%84%d9%85%d8%b4%d8%a7%d8%b1%d9%83%d8%a9/</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>وصل وزير الداخلية والبلديات أحمد الحجار إلى دولة قطر، للمشاركة في فعاليات المعرض العالمي للأمن الداخلي والسلامة “ميليبول قطر 2026″، بدعوة من وزير الداخلية وقائد قوة الأمن الداخلي “لخويا” الشيخ خليفة بن حمد بن خليفة آل ثاني.
+ومن المقرر أن يعقد الوزير الحجار سلسلة لقاءات مع عدد من المسؤولين ونظرائه المشاركين في المعرض، تتناول سبل تعزيز التعاون الأمني وتبادل الخبرات، والاطلاع على أحدث التقنيات والحلول في مجالات الأمن الداخلي والسلامة العامة.
+وفور وصوله إلى الدوحة، عقد الوزير الحجار لقاء مع وزير الداخلية ومكافحة المخدرات الباكستاني محسن نقوي، بحضور سفير لبنان في قطر بلال قبلان وأمين سر مجلس الأمن الداخلي المركزي العميد سامي ناصيف. وكانت مناسبة لجولة أفق حول التطورات الراهنة في المنطقة والمستجدات الإقليمية وانعكاساتها على الأمن والاستقرار.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:44.936637+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>الوزير الحجار وضع إكليلا من الزهر على ضريح اللواء الشهيد وسام الحسن</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d9%88%d8%b6%d8%b9-%d8%a5%d9%83%d9%84%d9%8a%d9%84%d8%a7-%d9%85%d9%86-%d8%a7%d9%84%d8%b2%d9%87%d8%b1-%d8%b9%d9%84%d9%89-%d8%b6/</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>وضع وزير الداخلية والبلديات أحمد الحجار، ممثلا بأمين سر مجلس الأمن الداخلي المركزي العميد سامي ناصيف، إكليلا من الزهر على ضريح اللواء الشهيد وسام الحسن، في ذكرى استشهاده، تقديرا لتضحياته وتضحيات رفيقه المؤهل أول أحمد صهيوني.
+وقال الوزير الحجار: في ذكرى استشهاد اللواء وسام الحسن، نستذكر رجلا كرّس حياته لحماية أمن لبنان وصون الدولة ومؤسساتها في مواجهة الأخطار .
+عهدنا أن نواصل العمل لحماية المواطنين وترسيخ سلطة الدولة وسيادتها، وفاء لدماء الشهداء وتضحياتهم.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:47.522494+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/17/</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>تشرين الأول 17, 2026 أخبار الوزير الحجار زار معرض بيروت الدولي للكتاب زار وزير الداخلية والبلديات أحمد الحجار معرض بيروت الدولي للكتاب، حيث جال على أجنحة المعرض، مطّلعًا على إصدارات دور النشر والفعاليات الثقافية المشاركة.كما شارك في حفل توقيع كتاب شقيقه العميد المتقاعد مجدي الحجار، بعنوان «نسقي بأحزاننا قصب النهر».</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:55.223850+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>الوزير الحجار زار معرض بيروت الدولي للكتاب</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%b2%d8%a7%d8%b1-%d9%85%d8%b9%d8%b1%d8%b6-%d8%a8%d9%8a%d8%b1%d9%88%d8%aa-%d8%a7%d9%84%d8%af%d9%88%d9%84%d9%8a-%d9%84%d9%84/</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>الوزير الحجار زار معرض بيروت الدولي للكتاب تشرين الأول 17, 2026 زار وزير الداخلية والبلديات أحمد الحجار معرض بيروت الدولي للكتاب، حيث جال على أجنحة المعرض، مطّلعًا على إصدارات دور النشر والفعاليات الثقافية المشاركة. كما شارك في حفل توقيع كتاب شقيقه العميد المتقاعد مجدي الحجار، بعنوان «نسقي بأحزاننا قصب النهر».</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:23:58.159243+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/16/</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، مجلس إدارة الصندوق التعاوني للمختارين في لبنان، برئاسة المختار ابراهيم حنا، في حضور المدير العام للصندوق جلال كبريت. وشكر الوفد الوزير الحجار على جهوده في دعم إصدار المرسوم المتعلق بتعويضات نهاية الخدمة للمختارين. وجرى خلال اللقاء البحث في شؤون الصندوق وأوضاع المختارين
+الوزير الحجار استقبل المدير العام للدفاع المدني العميد الركن عماد خريش
+استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، المدير العام للدفاع المدني العميد الركن عماد خريش، وبحث معه في أوضاع المديرية وحاجاتها، والجهود التي يبذلها العناصر والمتطوعون في الاستجابة للحوادث والطوارئ، مشددا على أهمية دورهم وضرورة دعم قدراتهم وتعزيز إمكاناتهم للقيام بالمهام الموكلة إليهم على أكمل وجه.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:00.697711+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل مجلس إدارة الصندوق التعاوني للمختارين في لبنان، برئاسة المختار ابراهيم حنا، في حضور المدير العام للصندوق جلال كبريت.</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d9%85%d8%ac%d9%84%d8%b3-%d8%a5%d8%af%d8%a7%d8%b1%d8%a9-%d8%a7%d9%84%d8%b5%d9%86%d8%af/</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، مجلس إدارة الصندوق التعاوني للمختارين في لبنان، برئاسة المختار ابراهيم حنا، في حضور المدير العام للصندوق جلال كبريت.
+وشكر الوفد الوزير الحجار على جهوده في دعم إصدار المرسوم المتعلق بتعويضات نهاية الخدمة للمختارين.
+وجرى خلال اللقاء البحث في شؤون الصندوق وأوضاع المختارين ومطالبهم.
+وأكد الوزير الحجار اهتمامه بمتابعتها والعمل على معالجتها وفق الأطر المتاحة.
+وشدد على أن المختارين يشكلون حلقة أساسية في خدمة المواطنين ، نظرا إلى دورهم في إنجاز المعاملات وتسهيل شؤونهم، موكدا أهمية التزام النزاهة والشفافية في أداء مهامهم.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:03.327129+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل المدير العام للدفاع المدني العميد الركن عماد خريش</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%85%d8%af%d9%8a%d8%b1-%d8%a7%d9%84%d8%b9%d8%a7%d9%85-%d9%84%d9%84%d8%af-4/</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، المدير العام للدفاع المدني العميد الركن عماد خريش، وبحث معه في أوضاع المديرية وحاجاتها، والجهود التي يبذلها العناصر والمتطوعون في الاستجابة للحوادث والطوارئ، مشددا على أهمية دورهم وضرورة دعم قدراتهم وتعزيز إمكاناتهم للقيام بالمهام الموكلة إليهم على أكمل وجه.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:05.956350+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/15/</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، رئيس بلدية جل الديب – بقنايا جورج زرد أبو جودة، واطّلع منه على سير العمل في البلدية والمشاريع التي تنفّذها، إضافة إلى أبرز التحديات التي تواجهها.كما جرى البحث في الشؤون الإنمائية والخدماتية للبلدة، وحاجات أبنائها، وسبل تعزيز العمل بما يسهم في تحسين</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:13.528254+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل رئيس بلدية جل الديب – بقنايا جورج زرد أبو جودة</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b1%d8%a6%d9%8a%d8%b3-%d8%a8%d9%84%d8%af%d9%8a%d8%a9-%d8%ac%d9%84-%d8%a7%d9%84%d8%af/</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، رئيس بلدية جل الديب – بقنايا جورج زرد أبو جودة، واطّلع منه على سير العمل في البلدية والمشاريع التي تنفّذها، إضافة إلى أبرز التحديات التي تواجهها.
+كما جرى البحث في الشؤون الإنمائية والخدماتية للبلدة، وحاجات أبنائها، وسبل تعزيز العمل بما يسهم في تحسين الخدمات المقدّمة إلى المواطنين ومواكبة متطلبات التنمية المحلية.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:16.445341+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/14/</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، المدير العام للأمن العام اللواء حسن شقير، وتم عرض الأوضاع الأمنية في البلاد.وشدد الوزير الحجار على أهمية تعزيز الإجراءات الأمنية والوقائية، ورفع مستوى التنسيق بين الأجهزة الأمنية لمنع أي تهديدات قد تمس أمن المواطنين وسلامتهم.كما تم التطرق إلى شؤون المديرية العامة للأمن
+الوزير أحمد الحجار ترأس مجلس الاستقرار (Stabilization project Board meeting)
+ترأس وزير الداخلية والبلديات أحمد الحجار اجتماع مجلس الاستقرار (Stabilization Board)، بمشاركة وفد من وزارة الخارجية الألمانية (GFFO) وبرنامج الأمم المتحدة الإنمائي (UNDP)، وحضور السفير الألماني توماس تسانايزن، الممثل المقيم لبرنامج الأمم المتحدة الإنمائي بالإنابة ثائر شريدي، محافظ لبنان الجنوبي والنبطية بالتكليف منصور ضو، المديرة العامة للأحوال الشخصية بالتكليف رودينا</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:19.060347+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل المدير العام للأمن العام اللواء حسن شقير ثم النائب جيمي جبور.</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%85%d8%af%d9%8a%d8%b1-%d8%a7%d9%84%d8%b9%d8%a7%d9%85-%d9%84%d9%84%d8%a3-7/</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، المدير العام للأمن العام اللواء حسن شقير، وتم عرض الأوضاع الأمنية في البلاد.
+وشدد الوزير الحجار على أهمية تعزيز الإجراءات الأمنية والوقائية، ورفع مستوى التنسيق بين الأجهزة الأمنية لمنع أي تهديدات قد تمس أمن المواطنين وسلامتهم.
+كما تم التطرق إلى شؤون المديرية العامة للأمن العام والمهام التي تضطلع بها، لا سيما في هذه المرحلة.
+واستقبل الوزير الحجار النائب جيمي جبور، وجرى البحث في الأوضاع العامة وشؤون إنمائية وخدماتية.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:21.695634+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>الوزير أحمد الحجار ترأس مجلس الاستقرار (Stabilization project Board meeting)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a3%d8%ad%d9%85%d8%af-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%aa%d8%b1%d8%a3%d8%b3-%d9%85%d8%ac%d9%84%d8%b3-%d8%a7%d9%84%d8%a7%d8%b3%d8%aa%d9%82%d8%b1%d8%a7/</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ترأس وزير الداخلية والبلديات أحمد الحجار اجتماع مجلس الاستقرار (Stabilization Board)، بمشاركة وفد من وزارة الخارجية الألمانية (GFFO) وبرنامج الأمم المتحدة الإنمائي (UNDP)، وحضور السفير الألماني توماس تسانايزن، الممثل المقيم لبرنامج الأمم المتحدة الإنمائي بالإنابة ثائر شريدي، محافظ لبنان الجنوبي والنبطية بالتكليف منصور ضو، المديرة العامة للأحوال الشخصية بالتكليف رودينا مرعب، رئيس مصلحة تسجيل السيارات والآليات بالتكليف العميد نزيه قبرصلي، ورئيس شعبة المعلوماتية في قوى الأمن الداخلي العميد علي سكيني.
+وخلال الاجتماع، تم البحث في سبل دعم حضور الدولة اللبنانية ومؤسساتها وتعزيز قدراتها في جنوب لبنان وبيروت والضاحية الجنوبية، لا سيما في المناطق المتأثرة بالحرب والاعتداءات الإسرائيلية والنزوح.
+كما تم الاطلاع على مشروع إعادة تأهيل مراكز قوى الأمن الداخلي ومنشآتها، بما يمكّنها من الاضطلاع بدورها في حفظ الأمن وتلبية حاجات المواطنين، بالتوازي مع دعم وتأهيل المؤسسات الرسمية التابعة لوزارة الداخلية والبلديات.
+وأكد الوزير الحجار أن “أولوية الحكومة تتمثل في بسط سلطة الدولة وتعزيز حضور مؤسساتها على كامل الأراضي اللبنانية، بما يكرّس الأمن والاستقرار ويعيد الثقة بقدرة الدولة على حماية المواطنين وخدمتهم”، مؤكدا أن “المرحلة الراهنة تتطلب تكامل الجهود لتعزيز الأمن، وتأمين الخدمات الأساسية، وتهيئة الظروف اللازمة لعودة الأهالي الآمنة والمستدامة إلى قراهم”.
+وتناول “أهمية هذا المشروع في مساندة جهود الدولة اللبنانية والاستجابة لحاجات المواطنين والمجتمعات المحلية”، مؤكدا أن “تعزيز حضور المؤسسات الرسمية، لا سيما الأجهزة الأمنية والإدارات المعنية، يشكل ركيزة أساسية في مسار التعافي وترسيخ الاستقرار”.
+وأشار الحجار إلى أنه يتابع “بصورة مستمرة، وبالتنسيق مع المديرية العامة لقوى الأمن الداخلي والمديرية العامة للأحوال الشخصية ومحافظة الجنوب وهيئة إدارة السير والآليات والمركبات، وبالتعاون مع المعنيين في برنامج الأمم المتحدة الإنمائي، سير العمل والتقدّم في تنفيذ المشروع، بما يضمن متابعة مراحله وتحقيق أهدافه”.
+وشكر لـ”وزارة الخارجية الألمانية وبرنامج الأمم المتحدة الإنمائي دعمهما وتمويلهما المشروع”، مثمّناً مساهمتهما، ومتمنيا “أن يشكل هذا التعاون، خطوة إضافية نحو تعزيز الاستقرار وتثبيت حضور الدولة ومؤسساتها”.
+وجدد الوزير الحجار “تأكيد تمسك الدولة بمواصلة الجهود الرامية إلى تحقيق الانسحاب الإسرائيلي، واستعادة حضورها الكامل في الجنوب، وبسط سلطتها بقواها الذاتية على الأراضي اللبنانية كافة”.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:27.216876+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/13/</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>حيّا وزير الداخلية والبلديات أحمد الحجار المديرية العامة لقوى الأمن الداخلي، مثمناً “جهود ضباط وعناصر حاجز ضهر البيدر، الذين تمكّنوا بفضل يقظتهم ومهنيتهم وجديّتهم في العمل من ضبط سيارة تحتوي على مواد متفجرة وتوقيف شخصين كانا على متنها”. واعتبر أن “هذه العملية تؤكد الدور المحوري الذي تضطلع به قوى الأمن</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:34.797489+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>الوزير الحجار ترأس إجتماع مجلس الأمن الداخلي المركزي: “رغم التحديات، لن نهدأ كأجهزة أمنية وجيش وقضاء، إلا بتأمين مستوى عال من الأمن”</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%aa%d8%b1%d8%a3%d8%b3-%d8%a5%d8%ac%d8%aa%d9%85%d8%a7%d8%b9-%d9%85%d8%ac%d9%84%d8%b3-%d8%a7%d9%84%d8%a3%d9%85%d9%86-%d8%a7/</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>حيّا وزير الداخلية والبلديات أحمد الحجار المديرية العامة لقوى الأمن الداخلي، مثمناً “جهود ضباط وعناصر حاجز ضهر البيدر، الذين تمكّنوا بفضل يقظتهم ومهنيتهم وجديّتهم في العمل من ضبط سيارة تحتوي على مواد متفجرة وتوقيف شخصين كانا على متنها”.
+واعتبر أن “هذه العملية تؤكد الدور المحوري الذي تضطلع به قوى الأمن الداخلي في كشف المخاطر الأمنية والتصدي لها قبل تحوّلها إلى تهديد فعلي للأمن والاستقرار”.
+وشدد وزير الداخلية، خلال ترؤسه اجتماع مجلس الأمن الداخلي المركزي، على أن يقظة ضباط قوى الأمن الداخلي وعناصرها، إلى جانب جاهزيتهم الميدانية، تجسدان أهمية الأمن الاستباقي في إحباط المخاطر”،
+وقال: “رغم التحديات، لن نهدأ كأجهزة أمنية وجيش وقضاء، إلا بتأمين مستوى عال من الأمن”.
+وأكد أن “أهمية ما كُشف عنه لا تقل عن أهمية استكمال التحقيقات لكشف ملابسات القضية كاملة”، مشيرا إلى أن “مخابرات الجيش اللبناني وشعبة المعلومات في قوى الأمن الداخلي ستتوليان التوسع في التحقيق، بناء على طلب النيابة العامة التمييزية، تمهيدا لكشف كل الملابسات ومحاسبة كل من يثبت تورّطه، وفقاً للقانون”.
+وجدّد الوزير الحجار “تأكيد ثقة الدولة باحترافية ضباط وعناصر سائر الأجهزة الأمنية والعسكرية، وبما يتمتعون به من قدرات لتقديم أفضل أداء”، لافتا إلى أن دورهم أساسي في حماية أمن اللبنانيين وتثبيت الاستقرار”.
+وفي هذا السياق، طلب من “الأجهزة الأمنية تشديد الإجراءات المتخذة عند نقاط التفتيش والحواجز، ورفع مستوى التدقيق وتعزيز الدوريات والوجود الأمني وتأمين الانتشار، بما يعزز القدرة على تحصين الأمن الداخلي”.
+ولفت الوزير الحجار إلى ان “عناصر حاجز ضهر البيدر كانوا اشتبهوا الاثنين الماضي، بسيارة من نوع «Dodge Caravan» رمادية اللون، بسبب حمولتها الزائدة، مما استدعى تفتيشها.
+وبنتيجة التفتيش، عُثر في داخلها على كمية من المواد المتفجرة، فتم توقيف السائق والشخص الذي كان برفقته، وإحالتهما مع المضبوطات إلى الشرطة العسكرية، بناءً على إشارة القضاء المختص”.
+هذا وتناول المجتمعون الأوضاع الأمنية في البلاد، وسبل تعزيز الإجراءات والتدابير الوقائية لمكافحة مختلف أنواع الجرائم، لا سيما تهريب المخدرات وترويجها وتعاطيها، إضافة إلى جرائم السرقة، بما يساهم في الحد من الأعمال المخالفة للقانون.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:37.695561+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/12/</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، النائب زياد حواط، وتم البحث في الأوضاع العامة وشؤون قضاء جبيل . كما استقبل النائب أحمد الخير، وجرى التداول في آخر المستجدات على الساحة الداخلية، إلى جانب عدد من الملفات الإنمائية والخدماتية. والتقى الحجار رئيس مجلس إدارة شركة تاتش المدير العام كريم</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:45.259512+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل النائبين زياد الحواط وأحمد الخير، والتقى رئيس مجلس إدارة «تاتش» المدير العام كريم سلام ثم محافظ عكار عماد لبكي.</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%86%d8%a7%d8%a6%d8%a8%d9%8a%d9%86-%d8%b2%d9%8a%d8%a7%d8%af-%d8%a7%d9%84/</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، النائب زياد حواط، وتم البحث في الأوضاع العامة وشؤون قضاء جبيل .
+كما استقبل النائب أحمد الخير، وجرى التداول في آخر المستجدات على الساحة الداخلية، إلى جانب عدد من الملفات الإنمائية والخدماتية.
+والتقى الحجار رئيس مجلس إدارة شركة تاتش المدير العام كريم سلام، وتم التداول في الملفات ذات الصلة بقطاع الاتصالات.
+واستقبل محافظ عكار عماد لبكي، وجرى عرض لملفات إدارية وتنموية تخص المحافظة.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:48.147936+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/10/</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>زار وزير الداخلية والبلديات أحمد الحجار معرض EXPERIA EXPO، الذي يشكّل مساحة تفاعلية تجمع الابتكار والتكنولوجيا، وتتيح التعرف إلى أحدث المشاريع والحلول الرقمية التي تطورها الشركات والمؤسسات المشاركة فيه. وتوقّف الوزير الحجار عند عدد من الأجنحة ، وكذلك جناح قوى الأمن الداخلي، حيث اطلع على أبرز التقنيات والتجهيزات المعتمدة في
+الوزير الحجار استقبل سفير ألمانيا في لبنان توماس تسانايزن.
+استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، سفير ألمانيا توماس تسانايزن في زيارة بروتوكولية لمناسبة تسلمه مهامه.وتم خلال اللقاء عرض التطورات في لبنان والمنطقة، والعلاقات الثنائية بين البلدين.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:50.916043+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>الوزير الحجار زار معرض EXPERIA EXPO</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%b2%d8%a7%d8%b1-%d9%85%d8%b9%d8%b1%d8%b6-experia-expo/</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>زار وزير الداخلية والبلديات أحمد الحجار معرض EXPERIA EXPO، الذي يشكّل مساحة تفاعلية تجمع الابتكار والتكنولوجيا، وتتيح التعرف إلى أحدث المشاريع والحلول الرقمية التي تطورها الشركات والمؤسسات المشاركة فيه.
+وتوقّف الوزير الحجار عند عدد من الأجنحة ، وكذلك جناح قوى الأمن الداخلي، حيث اطلع على أبرز التقنيات والتجهيزات المعتمدة في العمل الأمني.
+كما استمع الوزير الحجار إلى عرض مفصل حول المبادرات التي تقوم بها قوى الأمن الداخلي لتعزيز التواصل مع المواطنين ونشر الوعي المجتمعي من الجرائم الإلكترونية والابتزاز الرقمي ومخاطر المخدرات.
+وكانت للوزير الحجار مداخلة عن الخطط الموضوعة من قبل وزارة الداخلية والبلديات لتعزيز السلامة المرورية، وما تقوم به الوزارة والمديرية العامة لقوى الأمن الداخلي لتوعية المواطنين على ضرورة التزام قواعد السلامة.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:24:53.800654+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل سفير ألمانيا في لبنان توماس تسانايزن.</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b3%d9%81%d9%8a%d8%b1-%d8%a3%d9%84%d9%85%d8%a7%d9%86%d9%8a%d8%a7-%d9%81%d9%8a-%d9%84/</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل سفير ألمانيا في لبنان توماس تسانايزن. تشرين الأول 10, 2026 استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، سفير ألمانيا توماس تسانايزن في زيارة بروتوكولية لمناسبة تسلمه مهامه. وتم خلال اللقاء عرض التطورات في لبنان والمنطقة، والعلاقات الثنائية بين البلدين.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:01.565310+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/09/</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ترأس وزير الداخلية والبلديات أحمد الحجار، في مكتبه، الاجتماع الدوري لمتابعة التحضيرات في مطار الرئيس رينيه معوض – القليعات، والتدابير الأمنية لمواكبة إطلاق أولى الرحلات المرتقبة في تشرين الثاني المقبل، بالتنسيق مع الجهات المعنية. وجرى خلال الاجتماع استعراض مستوى الجهوزية الأمنية في المطار، والإجراءات والخطط الواجب استكمالها لتأمين حمايته وضمان</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:09.412631+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>الوزير الحجار ترأس الاجتماع الدوري لمتابعة التحضيرات في مطار الرئيس رينيه معوض – القليعات: الأجهزة الأمنية جاهزة لتأمين انطلاقة وتشغيل المطار.</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%aa%d8%b1%d8%a3%d8%b3-%d8%a7%d9%84%d8%a7%d8%ac%d8%aa%d9%85%d8%a7%d8%b9-%d8%a7%d9%84%d8%af%d9%88%d8%b1%d9%8a-%d9%84%d9%85/</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ترأس وزير الداخلية والبلديات أحمد الحجار، في مكتبه، الاجتماع الدوري لمتابعة التحضيرات في مطار الرئيس رينيه معوض – القليعات، والتدابير الأمنية لمواكبة إطلاق أولى الرحلات المرتقبة في تشرين الثاني المقبل، بالتنسيق مع الجهات المعنية.
+وجرى خلال الاجتماع استعراض مستوى الجهوزية الأمنية في المطار، والإجراءات والخطط الواجب استكمالها لتأمين حمايته وضمان سلامة المسافرين والوافدين والعاملين فيه، وأمن حركة الطيران، إضافة إلى تعزيز التنسيق والتكامل بين مختلف الأجهزة الأمنية والإدارات المعنية، بما يواكب متطلبات تشغيل المطار وفق المعايير المعتمدة.
+وأكد الوزير الحجار أن جهاز أمن المطار وسائر الأجهزة الأمنية التابعة لوزارة الداخلية والبلديات على جهوزية تامة لتأمين تشغيل المطار، وضمان انطلاقة آمنة ومنظمة لهذا المرفق الحيوي وذلك فور استكمال الأعمال الإنشائية والتجهيزات المطلوبة.
+وحضر الاجتماع، قائد جهاز أمن مطار رفيق الحريري الدولي – بيروت العميد الركن فادي كفوري، رئيس مجلس إدارة شركة Sky Lounges Services زياد الملا، قائد جهاز أمن السفارات والإدارات والمؤسسات العامة العميد الركن أحمد حمدان، قائد سرية مطار رفيق الحريري الدولي – بيروت في قوى الامن الداخلي العميد ياسر الميس، رئيس دائرة أمن عام مطار رفيق الحريري الدولي – بيروت العقيد جورج داغر، وممثل المديرية العامة للجمارك رئيس دائرة المسافرين في السوق الحرة المراقب أول شكري الحاج.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:12.287065+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/08/</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>تشرين الأول 8, 2026 أخبار الوزير الحجار استقبل النائب وليد البعريني، ثم الوزير السابق ناصر ياسين والشيخ محمد المغربي. استقبل وزير الداخلية والبلديات أحمد الحجار، النائب وليد البعريني، ثم الوزير السابق ناصر ياسين والشيخ محمد المغربي، وتم البحث في الاوضاع العامة في البلاد، وشؤون انمائية وخدماتية.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:19.780796+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل النائب وليد البعريني، ثم الوزير السابق ناصر ياسين والشيخ محمد المغربي.</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%86%d8%a7%d8%a6%d8%a8-%d9%88%d9%84%d9%8a%d8%af-%d8%a7%d9%84%d8%a8%d8%b9/</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل النائب وليد البعريني، ثم الوزير السابق ناصر ياسين والشيخ محمد المغربي. تشرين الأول 8, 2026 استقبل وزير الداخلية والبلديات أحمد الحجار، النائب وليد البعريني، ثم الوزير السابق ناصر ياسين والشيخ محمد المغربي، وتم البحث في الاوضاع العامة في البلاد، وشؤون انمائية وخدماتية.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:22.674352+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/07/</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، مساء اليوم، رئيس لجنة الإدارة والعدل النائب جورج عدوان. وخلال اللقاء، تم البحث في آخر المستجدات في البلاد، إلى جانب عدد من الملفات التشريعية والإدارية المشتركة المرتبطة بعمل الوزارة واللجنة، وشؤون إنمائية وخدماتية.
+الوزير الحجار استقبل الممثل المقيم لبرنامج الأمم المتحدة الإنمائي بالإنابة ثائر شريدي ثم رئيس بلدية الشيخ محمد ياسر طعوم مع وفد، والتقى رئيس الهيئة الوطنية لإدارة النفايات الصلبة مروان رزق الله.
+استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، الممثل المقيم لبرنامج الأمم المتحدة الإنمائي بالإنابة ثائر شريدي، وجرى البحث في التعاون القائم بين البرنامج والوزارة، والدعم الذي يقدمه إلى الأجهزة الأمنية والإدارية التابعة لها، لا سيما في إطار مشروع دعم التنمية المحلية، انطلاقا من الخطة الاستراتيجية لوزارة الداخلية والبلديات. كما</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:25.256988+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل رئيس لجنة الإدارة والعدل النائب جورج عدوان.</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b1%d8%a6%d9%8a%d8%b3-%d9%84%d8%ac%d9%86%d8%a9-%d8%a7%d9%84%d8%a5%d8%af%d8%a7%d8%b1/</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، مساء اليوم، رئيس لجنة الإدارة والعدل النائب جورج عدوان. وخلال اللقاء، تم البحث في آخر المستجدات في البلاد، إلى جانب عدد من الملفات التشريعية والإدارية المشتركة المرتبطة بعمل الوزارة واللجنة، وشؤون إنمائية وخدماتية.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:27.925382+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل الممثل المقيم لبرنامج الأمم المتحدة الإنمائي بالإنابة ثائر شريدي ثم رئيس بلدية الشيخ محمد ياسر طعوم مع وفد، والتقى رئيس الهيئة الوطنية لإدارة النفايات الصلبة مروان رزق الله.</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%85%d9%85%d8%ab%d9%84-%d8%a7%d9%84%d9%85%d9%82%d9%8a%d9%85-%d9%84%d8%a8/</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، الممثل المقيم لبرنامج الأمم المتحدة الإنمائي بالإنابة ثائر شريدي، وجرى البحث في التعاون القائم بين البرنامج والوزارة، والدعم الذي يقدمه إلى الأجهزة الأمنية والإدارية التابعة لها، لا سيما في إطار مشروع دعم التنمية المحلية، انطلاقا من الخطة الاستراتيجية لوزارة الداخلية والبلديات.
+كما استقبل رئيس بلدية الشيخ محمد ياسر طعوم، مع وفد، والذي عرض عددا من المطالب الإنمائية التي تهم المنطقة.
+والتقى الوزير الحجار رئيس الهيئة الوطنية لإدارة النفايات الصلبة مروان رزق الله، وتم البحث في واقع إدارة النفايات الصلبة، وعمل الهيئة وخطتها لإدارة هذا الملف. كما تم التطرق إلى سبل معالجة أزمة النفايات، لا سيما في منطقة الشمال وعكار، والعمل على إيجاد الحلول المستدامة.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:30.571304+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/06/</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، الوزير السابق محمد فهمي، وجرى عرض للأوضاع العامة في البلاد. واستقبل النائب وائل أبو فاعور، وتناول اللقاء المستجدات على الساحة الداخلية، وشؤونا انمائية وخدماتية. والتقى أيضا النائبة غادة أيوب، وجرى عرض للأوضاع وملفات خدماتية تتعلق بقضاء جزين .</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:40.906342+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل الوزير السابق محمد فهمي والتقى النائبين وائل أبو فاعور وغادة أيوب.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%b3%d8%a7%d8%a8%d9%82-%d9%85%d8%ad/</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، الوزير السابق محمد فهمي، وجرى عرض للأوضاع العامة في البلاد.
+واستقبل النائب وائل أبو فاعور، وتناول اللقاء المستجدات على الساحة الداخلية، وشؤونا انمائية وخدماتية.
+والتقى أيضا النائبة غادة أيوب، وجرى عرض للأوضاع وملفات خدماتية تتعلق بقضاء جزين .</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:43.795534+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/05/</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، مساء اليوم، وفدا من البلديات المجاورة لمكب سرار، واستمع إلى مطالبه وهواجس الاهالي، لا سيما ما يتعلق بإعادة فتح المكب. وحيّا الوزير الحجار الموقف الإيجابي للوفد، مؤكدا تفهمه لمطالب البلديات وحرصه على معالجتها، ووعد بمتابعة الموضوع بما يضمن حصول البلديات على حقوقها ولا سيما</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:51.352137+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل وفدا من البلديات المجاورة لمكب سرار.</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d9%88%d9%81%d8%af%d8%a7-%d9%85%d9%86-%d8%a7%d9%84%d8%a8%d9%84%d8%af%d9%8a%d8%a7%d8%aa/</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، مساء اليوم، وفدا من البلديات المجاورة لمكب سرار، واستمع إلى مطالبه وهواجس الاهالي، لا سيما ما يتعلق بإعادة فتح المكب.
+وحيّا الوزير الحجار الموقف الإيجابي للوفد، مؤكدا تفهمه لمطالب البلديات وحرصه على معالجتها، ووعد بمتابعة الموضوع بما يضمن حصول البلديات على حقوقها ولا سيما ما تستحقه من الصندوق البلدي المستقل.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:25:54.190421+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/02/</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>في زيارة للنبطية، أكد وزير الداخلية والبلديات أحمد الحجار أن “الدولة ستكون موجودة دائما إلى جانب المواطنين”، مشددا على أن “الجنوب ليس بخير”، وقال: “لذلك فإن كل لبنان ليس بخير، وأولوية الدولة المطلقة تحرير الجنوب وبسط سلطتها عبر قواها الذاتية من جيش وقوى أمنية حتى آخر ذرة من تراب الجنوب”.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:01.699420+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>الوزير الحجار رافق رئيس مجلس الوزراء القاضي نواف سلام في زيارة لمدينة النبطية</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%b1%d8%a7%d9%81%d9%82-%d8%b1%d8%a6%d9%8a%d8%b3-%d9%85%d8%ac%d9%84%d8%b3-%d8%a7%d9%84%d9%88%d8%b2%d8%b1%d8%a7%d8%a1-%d8%a7/</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>في زيارة للنبطية، أكد وزير الداخلية والبلديات أحمد الحجار أن “الدولة ستكون موجودة دائما إلى جانب المواطنين”، مشددا على أن “الجنوب ليس بخير”، وقال: “لذلك فإن كل لبنان ليس بخير، وأولوية الدولة المطلقة تحرير الجنوب وبسط سلطتها عبر قواها الذاتية من جيش وقوى أمنية حتى آخر ذرة من تراب الجنوب”.
+وكان الوزير الحجار رافق رئيس مجلس الوزراء القاضي نواف سلام في زيارة لمدينة النبطية، شارك فيها ايضا وزيرا المال ياسين جابر والعمل محمد حيدر وعدد من قادة الأجهزة الأمنية والدفاع المدني، إلى جانب نواب وفاعليات المنطقة.
+واستهلت الجولة بزيارة سرية درك النبطية في كفرجوز، حيث تم الاطلاع على أوضاع السرية ومهام عناصرها، وشدد الوزير الحجار على أن “تعزيز حضور الدولة والأجهزة الأمنية وانتشارها يشكلان أساسا لترسيخ الأمن والاستقرار”.
+ثم انتقل الوفد إلى بلدية النبطية، حيث عقد لقاء مع رئيس البلدية وفاعليات المدينة، وقال الوزير الحجار في كلمته: “نحن هنا لنقول إن الدولة معكم وأولويتها المطلقة تحرير الجنوب”.
+بعدها، انتقل الوفد، برفقة رئيس الحكومة، إلى موقع المقر الجديد للدفاع المدني، حيث تم وضع حجر الأساس للمبنى، في إطار دعم قدرات الدفاع المدني وتعزيز جهوزيته في منطقة النبطية والجنوب.
+كما شملت الزيارة مركز الأمن العام في النبطية بعد إنجاز أعمال تأهيله، إضافة إلى سرايا النبطية الحكومي بعد اجراء أعمال الترميم والتأهيل، في تأكيد على عودة مؤسسات الدولة إلى العمل في المدينة وتعزيز حضورها في خدمة المواطنين.
+واختتمت الجولة بزيارة إمام مدينة النبطية الشيخ عبد الحسين صادق في منزله، حيث تم البحث في أوضاع المدينة والمنطقة وحاجات أهلها، وتأكيد أهمية التعاون والتنسيق بما يعزز صمود أبناء الجنوب وحضور الدولة ومؤسساتها.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:04.595088+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/01/</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، وزير الاقتصاد والتجارة عامر البساط، في إطار اجتماعاتهما الدورية، وجرى البحث في تعزيز التعاون والتنسيق بين الوزارتين.كما تمت مناقشة عدد من الملفات المشتركة، وسبل توحيد الجهود لمعالجتها ومتابعة الإجراءات المطلوبة، ومواكبة حاجات المواطنين. والتقى الوزير الحجار النائبين ابراهيم منيمنة وملحم خلف،</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:12.150146+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل وزير الاقتصاد والتجارة عامر البساط، والتقى النائبين ابراهيم منيمنة وملحم خلف ثم النائب غسان حاصباني</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%a7%d9%82%d8%aa%d8%b5%d8%a7%d8%af-%d9%88%d8%a7-2/</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، وزير الاقتصاد والتجارة عامر البساط، في إطار اجتماعاتهما الدورية، وجرى البحث في تعزيز التعاون والتنسيق بين الوزارتين.
+كما تمت مناقشة عدد من الملفات المشتركة، وسبل توحيد الجهود لمعالجتها ومتابعة الإجراءات المطلوبة، ومواكبة حاجات المواطنين.
+والتقى الوزير الحجار النائبين ابراهيم منيمنة وملحم خلف، وجرى عرض الأوضاع العامة في البلاد، لا سيما القضايا التي تعني بيروت، وسبل معالجتها لما فيه مصلحة أبناء العاصمة.
+كما استقبل النائب غسان حاصباني، وتم البحث ايضا في شؤون العاصمة بيروت الإنمائية والخدماتية.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:15.081169+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/30/</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، مساء اليوم، المدير العام للأمن العام اللواء حسن شقير، واطلع منه على الأوضاع الأمنية في البلاد، وسير عمل المديرية في إطار الحفاظ على الأمن والاستقرار، وتسهيل معاملات المواطنين والمقيمين.واطلع اللواء شقير الوزير الحجار على إطلاق خدمة البصمة الإلكترونية لجواز السفر اللبناني في كل من
+الوزير الحجار استقبل النائب حيدر ناصر ثم النائب السابق عاطف مجدلاني والتقى رئيسة معهد باسل فليحان المالي والاقتصادي لميا مبيض البساط ثم رئيسة جمعية “بيروت ماراثون” مي الخليل.
+استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، النائب حيدر ناصر، وجرى البحث في الأوضاع العامة في البلاد. واستقبل النائب السابق عاطف مجدلاني. كما التقى الوزير الحجار رئيسة معهد باسل فليحان المالي والاقتصادي لميا مبيض البساط، وتم عرض عدد من المواضيع ذات الصلة بعمل المعهد، لا سيما في مجال</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:17.644327+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل المدير العام للأمن العام اللواء حسن شقير ثم رئيس مصلحة تسجيل السيارات والآليات بالتكليف العميد نزيه قبرصلي</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%85%d8%af%d9%8a%d8%b1-%d8%a7%d9%84%d8%b9%d8%a7%d9%85-%d9%84%d9%84%d8%a3-6/</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، مساء اليوم، المدير العام للأمن العام اللواء حسن شقير، واطلع منه على الأوضاع الأمنية في البلاد، وسير عمل المديرية في إطار الحفاظ على الأمن والاستقرار، وتسهيل معاملات المواطنين والمقيمين.
+واطلع اللواء شقير الوزير الحجار على إطلاق خدمة البصمة الإلكترونية لجواز السفر اللبناني في كل من ديترويت وواشنطن في الولايات المتحدة الأميركية، وأثنى الوزير الحجار على الجهود التي بذلتها المديرية العامة للأمن العام لتسهيل حصول اللبنانيين في الخارج على هذه الخدمة، بالتنسيق مع وزارة الخارجية والمغتربين.
+كما استقبل رئيس مصلحة تسجيل السيارات والآليات بالتكليف العميد نزيه قبرصلي، وجرى عرض سير العمل في المصلحة، والجهود المبذولة لتحسين مستوى الخدمات المقدمة.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:20.323542+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل النائب حيدر ناصر ثم النائب السابق عاطف مجدلاني والتقى رئيسة معهد باسل فليحان المالي والاقتصادي لميا مبيض البساط ثم رئيسة جمعية “بيروت ماراثون” مي الخليل.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%86%d8%a7%d8%a6%d8%a8-%d8%ad%d9%8a%d8%af%d8%b1-%d9%86%d8%a7%d8%b5%d8%b1/</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، النائب حيدر ناصر، وجرى البحث في الأوضاع العامة في البلاد.
+واستقبل النائب السابق عاطف مجدلاني.
+كما التقى الوزير الحجار رئيسة معهد باسل فليحان المالي والاقتصادي لميا مبيض البساط، وتم عرض عدد من المواضيع ذات الصلة بعمل المعهد، لا سيما في مجال تدريب البلديات وتعزيز قدراتها.
+كذلك، استقبل الوزير الحجار رئيسة جمعية “بيروت ماراثون” مي الخليل، واطلع منها على عمل الجمعية والتحضيرات الجارية لتنظيم السباق السنوي، وجرى التشديد على ضرورة الالتزام بشروط السلامة العامة واتخاذ التدابير اللازمة لضمان حسن سير السباق.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:22.976612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/29/</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، سفيرة تشيكيا استر لوفيرونا، وتم استعراض المستجدات السياسية على الساحتين الداخلية والإقليمية، إضافة إلى البحث في سبل تعزيز التعاون في مختلف المجالات. واستقبل النائب أحمد الخير ، ثم النائب محمد سليمان، وبحث مع كل منهما في الأوضاع العامة وشؤون إنمائية وخدماتية.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:30.480804+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل سفيرة تشيكيا استر لوفيرونا والتقى النائب أحمد الخير ، والنائب محمد سليمان ثم رئيس اتحاد بلديات قضاء بشري رئيس بلدية بقاعكفرا إيلي مخلوف.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b3%d9%81%d9%8a%d8%b1%d8%a9-%d8%aa%d8%b4%d9%8a%d9%83%d9%8a%d8%a7-%d8%a7%d8%b3%d8%aa/</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، سفيرة تشيكيا استر لوفيرونا، وتم استعراض المستجدات السياسية على الساحتين الداخلية والإقليمية، إضافة إلى البحث في سبل تعزيز التعاون في مختلف المجالات.
+واستقبل النائب أحمد الخير ، ثم النائب محمد سليمان، وبحث مع كل منهما في الأوضاع العامة وشؤون إنمائية وخدماتية.
+كما التقى رئيس اتحاد بلديات قضاء بشري رئيس بلدية بقاعكفرا إيلي مخلوف وتخلل اللقاء بحث في شؤون تهم القضاء.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:33.390199+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/28/</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، على التوالي، النواب قاسم هاشم، وأكرم شهيب ثم سيمون أبي رميا، وبحث مع كل منهم في الأوضاع العامة في البلاد والتطورات الراهنة، إلى جانب عدد من الملفات الانمائية والخدماتية. كما استقبل الوزير السابق ألان حكيم، وتم التداول في الأوضاع العامة. وبحث مع المديرة العامة
+الوزير الحجار استقبل رئيس اتحادات ونقابات قطاع النقل البري بسام طليس.
+استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، رئيس اتحادات ونقابات قطاع النقل البري بسام طليس، وبحث معه في أوضاع قطاع النقل البري.وأكد الوزير الحجار أن القوى الأمنية ستواصل متابعة المخالفات المتعلقة باللوحات العمومية، والسيارات والدراجات الآلية التي تعمل خلافا للقوانين والأنظمة المرعية الإجراء، إضافة إلى ملف العمالة غير</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:36.019675+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل نواباً والتقى والوزير السابق حكيم ثم المديرة العامة للشؤون السياسية واللاجئين فاتن يونس.</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d9%86%d9%88%d8%a7%d8%a8%d8%a7%d9%8b-%d9%88%d8%a7%d9%84%d8%aa%d9%82%d9%89-%d9%88%d8%a7/</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، على التوالي، النواب قاسم هاشم، وأكرم شهيب ثم سيمون أبي رميا، وبحث مع كل منهم في الأوضاع العامة في البلاد والتطورات الراهنة، إلى جانب عدد من الملفات الانمائية والخدماتية.
+كما استقبل الوزير السابق ألان حكيم، وتم التداول في الأوضاع العامة.
+وبحث مع المديرة العامة للشؤون السياسية واللاجئين في الوزارة فاتن يونس في عمل المديرية، ولا سيما ما يتعلق بملف الجمعيات ومتابعة أوضاعها.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:38.643099+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل رئيس اتحادات ونقابات قطاع النقل البري بسام طليس.</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b1%d8%a6%d9%8a%d8%b3-%d8%a7%d8%aa%d8%ad%d8%a7%d8%af%d8%a7%d8%aa-%d9%88%d9%86%d9%82/</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، رئيس اتحادات ونقابات قطاع النقل البري بسام طليس، وبحث معه في أوضاع قطاع النقل البري.
+وأكد الوزير الحجار أن القوى الأمنية ستواصل متابعة المخالفات المتعلقة باللوحات العمومية، والسيارات والدراجات الآلية التي تعمل خلافا للقوانين والأنظمة المرعية الإجراء، إضافة إلى ملف العمالة غير الشرعية في قطاع النقل العمومي.
+وفي هذا الإطار، طلب الوزير الحجار من المديرية العامة لقوى الأمن الداخلي استكمال الإجراءات اللازمة لضبط هذه المخالفات، ومواكبة الملف بصورة دائمة.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:41.310125+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/25/</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>أيلول 25, 2026 أخبار الوزير الحجار استقبل النائبة غادة أيوب. استقبل وزير الداخلية والبلديات أحمد الحجار في مكتبه اليوم النائبة غادة أيوب، وجرى عرض للتطورات الراهنة على الساحة الداخلية، وشؤون انمائية تتعلق بقضاء جزين.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:51.580632+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل النائبة غادة أيوب.</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%86%d8%a7%d8%a6%d8%a8%d8%a9-%d8%ba%d8%a7%d8%af%d8%a9-%d8%a3%d9%8a%d9%88/</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل النائبة غادة أيوب. أيلول 25, 2026 استقبل وزير الداخلية والبلديات أحمد الحجار في مكتبه اليوم النائبة غادة أيوب، وجرى عرض للتطورات الراهنة على الساحة الداخلية، وشؤون انمائية تتعلق بقضاء جزين.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:26:59.463073+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/24/</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>تابع وزير الداخلية والبلديات أحمد الحجار الوضع الأمني في البلاد مع المدير العام لقوى الأمن الداخلي اللواء رائد عبدالله، الذي أطّلعه على التدابير والإجراءات المتخذة للحفاظ على الأمن والنظام.وشدد الوزير الحجار على ضرورة رفع مستوى الإجراءات الأمنية، لا سيما في بيروت ومحيط طريق مطار رفيق الحريري الدولي – بيروت، بما</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:07.198205+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>الوزير الحجار تابع الوضع الأمني في البلاد مع المدير العام لقوى الأمن الداخلي اللواء رائد عبدالله، واستقبل النواب أمين شري، فيصل الصايغ ووليد البعريني، والتقى محافظ عكار مع وفد من بلديات عكارية.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%aa%d8%a7%d8%a8%d8%b9-%d8%a7%d9%84%d9%88%d8%b6%d8%b9-%d8%a7%d9%84%d8%a3%d9%85%d9%86%d9%8a-%d9%81%d9%8a-%d8%a7%d9%84%d8%a8/</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>تابع وزير الداخلية والبلديات أحمد الحجار الوضع الأمني في البلاد مع المدير العام لقوى الأمن الداخلي اللواء رائد عبدالله، الذي أطّلعه على التدابير والإجراءات المتخذة للحفاظ على الأمن والنظام.
+وشدد الوزير الحجار على ضرورة رفع مستوى الإجراءات الأمنية، لا سيما في بيروت ومحيط طريق مطار رفيق الحريري الدولي – بيروت، بما يضمن سلامة المواطنين ويعزز الاستقرار، إلى جانب مواصلة التشدد في ضبط مخالفات السير وتنظيم حركة المرور.
+وفي إطار متابعته للملفات المناطقية، استقبل الوزير الحجار، على التوالي، النواب أمين شري، فيصل الصايغ ووليد البعريني، وتناولت اللقاءات الأوضاع العامة في البلاد، إلى جانب شؤون مناطقهم والقضايا التي تعني المواطنين فيها.
+كذلك عقد الوزير الحجار اجتماعا مع محافظ عكار عماد لبكي حضره وفد من بلديات عكارية، واستمع إلى مطالبهم.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:10.142239+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/23/</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>أكد وزير الداخلية والبلديات أحمد الحجار أن البلديات شريك أساسي في متابعة شؤون المواطنين وتلبية حاجاتهم، مشددا على أن الوزارة لن تدخر جهدا في دعمها، بما يعزز قدرتها للاستجابة لمتطلبات الأهالي. وكان الوزير الحجار استقبل في مكتبه اليوم، وفدا من اتحاد بلديات بنت جبيل، واطلع منه على أوضاع البلدات وأهاليها</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:17.670251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل وفدا من اتحاد بلديات بنت جبيل ثم مفتي عكار الشيخ زيد بكار زكريا على رأس وفد.</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d9%88%d9%81%d8%af%d8%a7-%d9%85%d9%86-%d8%a7%d8%aa%d8%ad%d8%a7%d8%af-%d8%a8%d9%84%d8%af-2/</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>أكد وزير الداخلية والبلديات أحمد الحجار أن البلديات شريك أساسي في متابعة شؤون المواطنين وتلبية حاجاتهم، مشددا على أن الوزارة لن تدخر جهدا في دعمها، بما يعزز قدرتها للاستجابة لمتطلبات الأهالي.
+وكان الوزير الحجار استقبل في مكتبه اليوم، وفدا من اتحاد بلديات بنت جبيل، واطلع منه على أوضاع البلدات وأهاليها والنازحين منها، في ظل استمرار الاعتداءات الإسرائيلية، والحاجات القائمة على مختلف المستويات.
+وأكد الوزير الحجار دعم الوزارة للبلديات ومتابعتها للملفات المرتبطة بها، لا سيما موضوع الصندوق البلدي المستقل وتوزيع العائدات المستحقة للبلديات، بما يساهم في تمكين المجالس البلدية من القيام بمهامها وتأمين الخدمات للمواطنين.
+كما استقبل الوزير الحجار مفتي عكار الشيخ زيد بكار زكريا على رأس وفد، وتم التداول في شؤون المنطقة وحاجات المواطنين فيها.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:20.553689+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/22/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، رئيس لجنة الدفاع الوطني والداخلية والبلديات النائب جهاد الصمد، وتم البحث في الأوضاع العامة والتطورات على الساحتين الداخلية والإقليمية.كما تناول اللقاء عددا من الملفات ذات الاهتمام المشترك، لا سيما المواضيع التي تتم متابعتها بالتنسيق بين وزارة الداخلية والبلديات ولجنة الدفاع الوطني</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:28.072659+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل رئيس لجنة الدفاع الوطني والداخلية والبلديات النائب جهاد الصمد.</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b1%d8%a6%d9%8a%d8%b3-%d9%84%d8%ac%d9%86%d8%a9-%d8%a7%d9%84%d8%af%d9%81%d8%a7%d8%b9-2/</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه اليوم، رئيس لجنة الدفاع الوطني والداخلية والبلديات النائب جهاد الصمد، وتم البحث في الأوضاع العامة والتطورات على الساحتين الداخلية والإقليمية.
+كما تناول اللقاء عددا من الملفات ذات الاهتمام المشترك، لا سيما المواضيع التي تتم متابعتها بالتنسيق بين وزارة الداخلية والبلديات ولجنة الدفاع الوطني والداخلية والبلديات النيابية، إضافة إلى شؤون إنمائية وخدماتية.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:31.271431+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/21/</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار رئيس جهاز أمن مطار رفيق الحريري الدولي – بيروت العميد الركن فادي كفوري واطلع منه على الواقع الأمني في المطار، والإجراءات المتخذة لضبط حركة المسافرين وتعزيز الرقابة والتفتيش، بما يؤمن أعلى مستويات الأمن والسلامة.وتناول البحث أيضا الترتيبات الأمنية المرتبطة بمطار رينيه معوض – القليعات،</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:38.784077+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل رئيس جهاز أمن مطار رفيق الحريري الدولي – بيروت العميد الركن فادي كفوري، والتقى رئيس لجنة المال والموازنة النائب ابراهيم كنعان.</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%b1%d8%a6%d9%8a%d8%b3-%d8%ac%d9%87%d8%a7%d8%b2-%d8%a3%d9%85%d9%86-%d9%85%d8%b7%d8%a7/</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار رئيس جهاز أمن مطار رفيق الحريري الدولي – بيروت العميد الركن فادي كفوري واطلع منه على الواقع الأمني في المطار، والإجراءات المتخذة لضبط حركة المسافرين وتعزيز الرقابة والتفتيش، بما يؤمن أعلى مستويات الأمن والسلامة.
+وتناول البحث أيضا الترتيبات الأمنية المرتبطة بمطار رينيه معوض – القليعات، والتحضيرات الجارية لمواكبة انطلاقة العمل فيه.
+كما استقبل الوزير الحجار رئيس لجنة المال والموازنة النائب ابراهيم كنعان، وجرى عرض الأوضاع العامة على الساحة الداخلية وشؤون انمائية وخدماتية.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:41.735473+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/19/</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>زار وزير الداخلية والبلديات أحمد الحجار ووزير الثقافة غسان سلامة الموقع الأثري في بلدة شحيم، في حضور النائب بلال عبدالله، والنائب السابق محمد الحجار، والمدير العام للآثار سركيس الخوري، ورئيس بلدية شحيم طارق شعبان، وأعضاء المجلس البلدي، إلى جانب حشد من فاعليات شحيم والجوار. وأعرب الوزير الحجار عن تقديره للوزير</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:49.242703+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>الوزير الحجار زار ووزير الثقافة غسان سلامة الموقع الأثري في بلدة شحيم.</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%b2%d8%a7%d8%b1-%d9%88%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ab%d9%82%d8%a7%d9%81%d8%a9-%d8%ba%d8%b3%d8%a7%d9%86-%d8%b3/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>زار وزير الداخلية والبلديات أحمد الحجار ووزير الثقافة غسان سلامة الموقع الأثري في بلدة شحيم، في حضور النائب بلال عبدالله، والنائب السابق محمد الحجار، والمدير العام للآثار سركيس الخوري، ورئيس بلدية شحيم طارق شعبان، وأعضاء المجلس البلدي، إلى جانب حشد من فاعليات شحيم والجوار.
+وأعرب الوزير الحجار عن تقديره للوزير سلامة على تعاونه واهتمامه الدائم بكل ما يتصل ببلدة شحيم، مؤكدا أن وجوده اليوم في البلدة يشكل دليلا على هذا الاهتمام.
+وقال: «نشكر الوزير سلامة على اهتمامه منذ البداية بكل ما يتعلق ببلدتنا، وعلى جهوده في تطوير هذا الموقع الأثري. والأهم بالنسبة إلينا هو الحفاظ على تاريخ شحيم، هذا التاريخ الغني والزاخر بالنجاحات، والذي تشهد عليه آثارها وما تركته الحضارات المتعاقبة فيها».
+وأكد أن «الغنى الحقيقي لشحيم هو في أبنائها ونجاحاتهم، وهو ما نعتز به ونفخر به دائماً».</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:52.100853+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/18/</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>عقد وزير الداخلية والبلديات أحمد الحجار، ووزير العمل محمد حيدر، ووزير الأشغال العامة والنقل فايز رسامني، اجتماعا تنسيقيا في وزارة الداخلية والبلديات، في حضور عدد من المعنيين، خُصّص للبحث في الإجراءات المتعلقة بعمل الشاحنات.وتناول البحث واقع قطاع الشاحنات، إضافة إلى وضع آلية تنسيق مشتركة بين الوزارات المعنية لمعالجة المسائل المطروحة</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:27:59.669780+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>إجتماع وزاري في وزارة الداخلية والبلديات للبحث في الإجراءات المتعلقة بعمل الشاحنات</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a5%d8%ac%d8%aa%d9%85%d8%a7%d8%b9-%d9%88%d8%b2%d8%a7%d8%b1%d9%8a-%d9%81%d9%8a-%d9%88%d8%b2%d8%a7%d8%b1%d8%a9-%d8%a7%d9%84%d8%af%d8%a7%d8%ae%d9%84%d9%8a%d8%a9-%d9%88%d8%a7%d9%84%d8%a8%d9%84%d8%af/</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>عقد وزير الداخلية والبلديات أحمد الحجار، ووزير العمل محمد حيدر، ووزير الأشغال العامة والنقل فايز رسامني، اجتماعا تنسيقيا في وزارة الداخلية والبلديات، في حضور عدد من المعنيين، خُصّص للبحث في الإجراءات المتعلقة بعمل الشاحنات.
+وتناول البحث واقع قطاع الشاحنات، إضافة إلى وضع آلية تنسيق مشتركة بين الوزارات المعنية لمعالجة المسائل المطروحة وفق القوانين والأنظمة المرعية الإجراء.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:02.521817+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/16/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>اختتم وزير الداخلية والبلديات أحمد الحجار زيارته الرسمية لإسلام آباد، بجولة شملت مؤسسات أمنية وتقنية باكستانية، واطلع خلالها على التجارب والخبرات الباكستانية في هذه المجالات. وفي هذا السياق، زار الوزير الحجار والوفد اللبناني المرافق المقر العام لقوة مكافحة المخدرات الباكستانية (ANF)، حيث اطلع على آليات عملها وجهودها في مجال مكافحة</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:10.286153+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>الوزير الحجار اختتم زيارته الرسمية لإسلام آباد، بجولة شملت مؤسسات أمنية وتقنية باكستانية.</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%ae%d8%aa%d8%aa%d9%85-%d8%b2%d9%8a%d8%a7%d8%b1%d8%aa%d9%87-%d8%a7%d9%84%d8%b1%d8%b3%d9%85%d9%8a%d8%a9-%d9%84%d8%a5/</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>اختتم وزير الداخلية والبلديات أحمد الحجار زيارته الرسمية لإسلام آباد، بجولة شملت مؤسسات أمنية وتقنية باكستانية، واطلع خلالها على التجارب والخبرات الباكستانية في هذه المجالات.
+وفي هذا السياق، زار الوزير الحجار والوفد اللبناني المرافق المقر العام لقوة مكافحة المخدرات الباكستانية (ANF)، حيث اطلع على آليات عملها وجهودها في مجال مكافحة المخدرات، لا سيما في ما يتصل بتعزيز القدرات الأمنية وتبادل الخبرات.
+وبعدها، انتقل إلى الهيئة الوطنية لقاعدة البيانات والتسجيل (NADRA)، التي تُعد جهة محورية في مجال الحوكمة الرقمية، وإدارة قواعد البيانات الوطنية، وتقديم خدمات موثوقة وآمنة إلى المواطنين في مختلف أنحاء باكستان، حيث استمع إلى شرح مفصل عن تجربتها في التحول الرقمي وتطوير الخدمات الحكومية.
+كما شملت الجولة الحديقة الوطنية لعلوم وتكنولوجيا الفضاء والطيران (NASTP)، حيث تعرّف الوزير الحجار والوفد المرافق إلى أبرز البرامج والمشاريع في مجالات علوم الفضاء والطيران والتكنولوجيا، ودور المركز في دعم الابتكار وتطوير القدرات التقنية.
+وتأتي هذه الجولة في ختام الزيارة الرسمية للوزير الحجار إلى باكستان، التي تضمنت سلسلة لقاءات مع كبار المسؤولين والقيادات السياسية والأمنية، وأبرزهم رئيس الجمهورية، ورئيس الحكومة، ووزيري الداخلية ومكافحة المخدرات والخارجية، وقائد الجيش وئيس مجلس الشيوخ، وهدفت كلها إلى تعزيز العلاقات الثنائية وتوسيع مجالات التعاون بين لبنان وباكستان.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:13.180654+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/09/15/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>واصل وزير الداخلية والبلديات أحمد الحجار لقاءاته الرسمية في إسلام آباد، فالتقى رئيس مجلس الشيوخ الباكستاني يوسف رضا جيلاني، ثم وزير الخارجية الباكستاني محمد إسحاق دار. وشكّل اللقاءان مناسبة لتبادل وجهات النظر حول التطورات الراهنة في المنطقة، والجهود المبذولة لتعزيز الاستقرار وفتح مسارات للحوار، مع تأكيد الجانب الباكستاني دعمه للبنان
+رئيس جمهورية باكستان الإسلامية آصف علي زرداري استقبل في إسلام آباد، وزير الداخلية والبلديات أحمد الحجار.
+استقبل رئيس جمهورية باكستان الإسلامية آصف علي زرداري، في إسلام آباد، وزير الداخلية والبلديات أحمد الحجار، في حضور الوفد اللبناني المرافق، وتناول اللقاء التطورات الراهنة في المنطقة، والجهود التي تبذلها باكستان للمساهمة في تعزيز الاستقرار الإقليمي وفتح قنوات الحوار بين الأطراف، إضافة إلى دورها في دعم المساعي الديبلوماسية الهادفة إلى
+الوزير الحجار التقى، في إطار زيارته الرسمية لإسلام آباد، رئيس الوزراء الباكستاني محمد شهباز شريف.
+التقى وزير الداخلية والبلديات أحمد الحجار، في إطار زيارته الرسمية لإسلام آباد، رئيس الوزراء الباكستاني محمد شهباز شريف. وخلال اللقاء، نقل الوزير الحجار تحيات رئيس الحكومة نواف سلام، مؤكدا رغبة لبنان في تعزيز التعاون الثنائي مع باكستان، وتطوير العلاقات بين البلدين في مختلف المجالات، لا سيما في المجال الأمني، بما</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:15.874628+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>واصل وزير الداخلية والبلديات أحمد الحجار لقاءاته الرسمية في إسلام آباد، فالتقى رئيس مجلس الشيوخ الباكستاني يوسف رضا جيلاني، ثم وزير الخارجية الباكستاني محمد إسحاق دار.</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d9%88%d8%a7%d8%b5%d9%84-%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%af%d8%a7%d8%ae%d9%84%d9%8a%d8%a9-%d9%88%d8%a7%d9%84%d8%a8%d9%84%d8%af%d9%8a%d8%a7%d8%aa-%d8%a3%d8%ad%d9%85%d8%af-%d8%a7%d9%84%d8%ad/</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>واصل وزير الداخلية والبلديات أحمد الحجار لقاءاته الرسمية في إسلام آباد، فالتقى رئيس مجلس الشيوخ الباكستاني يوسف رضا جيلاني، ثم وزير الخارجية الباكستاني محمد إسحاق دار.
+وشكّل اللقاءان مناسبة لتبادل وجهات النظر حول التطورات الراهنة في المنطقة، والجهود المبذولة لتعزيز الاستقرار وفتح مسارات للحوار، مع تأكيد الجانب الباكستاني دعمه للبنان وحرصه على استقراره وسيادته.
+كما جرى التشديد على أهمية استمرار التواصل والتنسيق بين البلدين، بما يعزز العلاقات الثنائية ويفتح آفاقا جديدة للتعاون في المجالات المشتركة.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:18.530957+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ministry_of_Interior_and_Municipalities.xlsx
+++ b/Ministry_of_Interior_and_Municipalities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3504,6 +3504,63 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/29/</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>تعمّم وزارتي الداخلية والبلديات والسياحة القرار المشترك المتعلق بتعديل قيمة التعرفة الرسمية لبدل الخدمة لراكني السيارات، بحيث أصبحت محددة بسقف أقصى قدره 500,000 ليرة لبنانية (خمسمائة ألف ليرة) لبدل خدمة ركن السيارات.
+الوزير الحجار استقبل المدير العام للأمن العام اللواء حسن شقير.
+استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، المدير العام للأمن العام اللواء حسن شقير، وتناول معه الملفات الأمنية والإدارية المرتبطة بعمل المديرية، في ضوء التطورات الراهنة.وجرى عرض للإجراءات الأمنية لمكافحة كل ما من شأنه المساس بالأمن والاستقرار، والتدابير الوقائية والاستباقية المتخذة، إضافة إلى الشؤون الإدارية في المديرية والمهام التي</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:25:24.997536+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل المدير العام للأمن العام اللواء حسن شقير.</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%85%d8%af%d9%8a%d8%b1-%d8%a7%d9%84%d8%b9%d8%a7%d9%85-%d9%84%d9%84%d8%a3-8/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، المدير العام للأمن العام اللواء حسن شقير، وتناول معه الملفات الأمنية والإدارية المرتبطة بعمل المديرية، في ضوء التطورات الراهنة.
+وجرى عرض للإجراءات الأمنية لمكافحة كل ما من شأنه المساس بالأمن والاستقرار، والتدابير الوقائية والاستباقية المتخذة، إضافة إلى الشؤون الإدارية في المديرية والمهام التي تضطلع بها.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:25:27.696765+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ministry_of_Interior_and_Municipalities.xlsx
+++ b/Ministry_of_Interior_and_Municipalities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3561,6 +3561,91 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الداخلية والبلديات في الجمهورية اللبنانية</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/2026/10/30/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، النائب نبيل بدر، وعرض معه للأوضاع العامة في البلاد، إلى جانب الشؤون الإنمائية والخدماتية في العاصمة بيروت.
+الوزير الحجار استقبل المدير العام لقوى الأمن الداخلي اللواء رائد عبد الله ورئيس شعبة المعلومات في قوى الأمن الداخلي العميد محمود قبرصلي
+استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، المدير العام لقوى الأمن الداخلي اللواء رائد عبد الله ورئيس شعبة المعلومات في قوى الأمن الداخلي العميد محمود قبرصلي، وتم البحث في الأوضاع الأمنية والإجراءات المتخذة للحفاظ على الأمن والاستقرار.وأثنى الوزير الحجار على “الجهود التي تبذلها المديرية العامة لقوى الأمن الداخلي والقطعات</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:57:58.696822+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل النائب نبيل بدر.</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%86%d8%a7%d8%a6%d8%a8-%d9%86%d8%a8%d9%8a%d9%84-%d8%a8%d8%af%d8%b1/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل النائب نبيل بدر. تشرين الأول 30, 2026 استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، النائب نبيل بدر، وعرض معه للأوضاع العامة في البلاد، إلى جانب الشؤون الإنمائية والخدماتية في العاصمة بيروت.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:58:08.912049+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>الوزير الحجار استقبل المدير العام لقوى الأمن الداخلي اللواء رائد عبد الله ورئيس شعبة المعلومات في قوى الأمن الداخلي العميد محمود قبرصلي</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://moim.gov.lb/%d8%a7%d9%84%d9%88%d8%b2%d9%8a%d8%b1-%d8%a7%d9%84%d8%ad%d8%ac%d8%a7%d8%b1-%d8%a7%d8%b3%d8%aa%d9%82%d8%a8%d9%84-%d8%a7%d9%84%d9%85%d8%af%d9%8a%d8%b1-%d8%a7%d9%84%d8%b9%d8%a7%d9%85-%d9%84%d9%82%d9%88-6/</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>استقبل وزير الداخلية والبلديات أحمد الحجار، في مكتبه، المدير العام لقوى الأمن الداخلي اللواء رائد عبد الله ورئيس شعبة المعلومات في قوى الأمن الداخلي العميد محمود قبرصلي، وتم البحث في الأوضاع الأمنية والإجراءات المتخذة للحفاظ على الأمن والاستقرار.
+وأثنى الوزير الحجار على “الجهود التي تبذلها المديرية العامة لقوى الأمن الداخلي والقطعات التابعة لها في متابعة الملفات الأمنية وملاحقة المطلوبين”، مشيدا بـ”الجهود الاستقصائية التي أدّت إلى توقيف قاتل الأب سمير ضو في جبيل”.
+وشدد على “أهمية تعزيز العمل الأمني الاستباقي، ورفع مستوى الجهوزية وتكثيف المتابعة الميدانية والاستقصائية، بما يسهم في كشف الجرائم وملاحقة مرتكبيها، وصون أمن المواطنين وسلامتهم”.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:58:11.893003+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
